--- a/data/SALARY OLD NKPL.xlsx
+++ b/data/SALARY OLD NKPL.xlsx
@@ -16987,10 +16987,10 @@
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" s="7">
-        <f>30-F3</f>
+        <f>31-F3</f>
         <v>0</v>
       </c>
       <c r="H3" s="7"/>
@@ -17002,12 +17002,12 @@
         <v>19500</v>
       </c>
       <c r="L3" s="8">
-        <f>ROUND(K3/30,0)</f>
-        <v>650</v>
+        <f>ROUND(K3/31,0)</f>
+        <v>629</v>
       </c>
       <c r="M3" s="8">
-        <f>ROUND(N3/30,0)</f>
-        <v>223</v>
+        <f>ROUND(N3/31,0)</f>
+        <v>216</v>
       </c>
       <c r="N3" s="9">
         <f>1000+1000+2000+700+2000</f>
@@ -17015,17 +17015,17 @@
       </c>
       <c r="O3" s="8">
         <f>L3*F3</f>
-        <v>19500</v>
+        <v>19499</v>
       </c>
       <c r="P3" s="8">
         <f>O3*1</f>
-        <v>19500</v>
+        <v>19499</v>
       </c>
       <c r="Q3" s="10">
         <v>0</v>
       </c>
       <c r="R3" s="8">
-        <f>(1000+1000+2000+700+2000)/30*F3</f>
+        <f>(1000+1000+2000+700+2000)/31*F3</f>
         <v>6700</v>
       </c>
       <c r="S3" s="9">
@@ -17035,7 +17035,7 @@
       <c r="T3" s="8"/>
       <c r="U3" s="8">
         <f t="shared" ref="U3:U37" si="1">P3+Q3+S3+R3+T3</f>
-        <v>26200</v>
+        <v>26199</v>
       </c>
       <c r="V3" s="10">
         <v>0</v>
@@ -17050,7 +17050,7 @@
       </c>
       <c r="Y3" s="8">
         <f>U3-W3-X3</f>
-        <v>26200</v>
+        <v>26199</v>
       </c>
       <c r="Z3" s="11">
         <f>IF(U3&gt;40000,200,IF(U3&gt;25000,150,IF(U3&gt;15000,130,IF(U3&gt;10000,110,0))))</f>
@@ -17064,7 +17064,7 @@
       <c r="AD3" s="10"/>
       <c r="AE3" s="13">
         <f>U3-W3-X3-Z3-AB3</f>
-        <v>26050</v>
+        <v>26049</v>
       </c>
       <c r="AF3" s="14"/>
     </row>
@@ -17083,76 +17083,77 @@
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="7">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G4" s="7">
-        <f t="shared" ref="G4:G52" si="2">30-F4</f>
-        <v>3</v>
+        <f t="shared" ref="G4:G52" si="2">31-F4</f>
+        <v>1</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6">
-        <v>13500</v>
+        <f>13500+500</f>
+        <v>14000</v>
       </c>
       <c r="K4" s="6">
         <f>11000</f>
         <v>11000</v>
       </c>
       <c r="L4" s="8">
-        <f t="shared" ref="L4:L12" si="3">K4/30</f>
-        <v>366.66666666666669</v>
+        <f t="shared" ref="L4:L14" si="3">ROUND(K4/31,0)</f>
+        <v>355</v>
       </c>
       <c r="M4" s="8">
-        <f>N4/30</f>
-        <v>83.333333333333329</v>
+        <f t="shared" ref="M4:M14" si="4">ROUND(N4/31,0)</f>
+        <v>97</v>
       </c>
       <c r="N4" s="16">
-        <f>2000+500</f>
-        <v>2500</v>
+        <f>2000+500+500</f>
+        <v>3000</v>
       </c>
       <c r="O4" s="13">
-        <f t="shared" ref="O4:O23" si="4">L4*F4</f>
-        <v>9900</v>
+        <f t="shared" ref="O4:O23" si="5">L4*F4</f>
+        <v>10650</v>
       </c>
       <c r="P4" s="13">
         <f>O4*0.7</f>
-        <v>6930</v>
+        <v>7454.9999999999991</v>
       </c>
       <c r="Q4" s="13">
-        <f t="shared" ref="Q4:Q5" si="5">O4*0.3</f>
-        <v>2970</v>
+        <f t="shared" ref="Q4:Q5" si="6">O4*0.3</f>
+        <v>3195</v>
       </c>
       <c r="R4" s="13">
-        <f>(1000+600+400+500)/30*F4</f>
-        <v>2250</v>
+        <f>(1000+600+400+500)/31*F4</f>
+        <v>2419.3548387096771</v>
       </c>
       <c r="S4" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>(L4+M4)*H4+500</f>
+        <v>500</v>
       </c>
       <c r="T4" s="13"/>
       <c r="U4" s="8">
         <f t="shared" si="1"/>
-        <v>12150</v>
+        <v>13569.354838709678</v>
       </c>
       <c r="V4" s="13">
         <f>P4</f>
-        <v>6930</v>
+        <v>7454.9999999999991</v>
       </c>
       <c r="W4" s="13">
         <f>ROUND(IF(V4&lt;=15000,V4*12%,IF(V4&gt;15000,0)),0)</f>
-        <v>832</v>
+        <v>895</v>
       </c>
       <c r="X4" s="8">
-        <f t="shared" ref="X4:X52" si="6">IF(J4&lt;=21000,ROUNDUP(O4*0.75%,0),0)</f>
-        <v>75</v>
+        <f t="shared" ref="X4:X52" si="7">IF(J4&lt;=21000,ROUNDUP(O4*0.75%,0),0)</f>
+        <v>80</v>
       </c>
       <c r="Y4" s="8">
-        <f t="shared" ref="Y4:Y51" si="7">U4-W4-X4</f>
-        <v>11243</v>
+        <f t="shared" ref="Y4:Y51" si="8">U4-W4-X4</f>
+        <v>12594.354838709678</v>
       </c>
       <c r="Z4" s="11">
-        <f t="shared" ref="Z4:Z51" si="8">IF(U4&gt;40000,200,IF(U4&gt;25000,150,IF(U4&gt;15000,130,IF(U4&gt;10000,110,0))))</f>
+        <f t="shared" ref="Z4:Z51" si="9">IF(U4&gt;40000,200,IF(U4&gt;25000,150,IF(U4&gt;15000,130,IF(U4&gt;10000,110,0))))</f>
         <v>110</v>
       </c>
       <c r="AA4" s="17">
@@ -17163,7 +17164,7 @@
       <c r="AD4" s="18"/>
       <c r="AE4" s="13">
         <f>U4-W4-X4-Z4-AB4</f>
-        <v>11133</v>
+        <v>12484.354838709678</v>
       </c>
       <c r="AF4" s="14"/>
     </row>
@@ -17182,7 +17183,7 @@
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5" s="7">
         <f t="shared" si="2"/>
@@ -17199,30 +17200,30 @@
       </c>
       <c r="L5" s="8">
         <f t="shared" si="3"/>
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="M5" s="8">
-        <f t="shared" ref="M5:M12" si="9">N5/30</f>
-        <v>165</v>
+        <f t="shared" si="4"/>
+        <v>160</v>
       </c>
       <c r="N5" s="9">
         <f>1000+1000+1500+700+750</f>
         <v>4950</v>
       </c>
       <c r="O5" s="8">
-        <f t="shared" si="4"/>
-        <v>12000</v>
+        <f t="shared" si="5"/>
+        <v>11997</v>
       </c>
       <c r="P5" s="8">
         <f>O5*0.7</f>
-        <v>8400</v>
+        <v>8397.9</v>
       </c>
       <c r="Q5" s="13">
-        <f t="shared" si="5"/>
-        <v>3600</v>
+        <f t="shared" si="6"/>
+        <v>3599.1</v>
       </c>
       <c r="R5" s="8">
-        <f>(1000+1000+1500+700+750)/30*F5</f>
+        <f>(1000+1000+1500+700+750)/31*F5</f>
         <v>4950</v>
       </c>
       <c r="S5" s="9">
@@ -17232,26 +17233,26 @@
       <c r="T5" s="8"/>
       <c r="U5" s="8">
         <f t="shared" si="1"/>
-        <v>16950</v>
+        <v>16947</v>
       </c>
       <c r="V5" s="8">
         <f>P5</f>
-        <v>8400</v>
+        <v>8397.9</v>
       </c>
       <c r="W5" s="8">
         <f>ROUND(IF(V5&lt;=15000,V5*12%,IF(V5&gt;15000,0)),0)</f>
         <v>1008</v>
       </c>
       <c r="X5" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>90</v>
       </c>
       <c r="Y5" s="8">
-        <f t="shared" si="7"/>
-        <v>15852</v>
+        <f t="shared" si="8"/>
+        <v>15849</v>
       </c>
       <c r="Z5" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>130</v>
       </c>
       <c r="AA5" s="17">
@@ -17262,7 +17263,7 @@
       <c r="AD5" s="10"/>
       <c r="AE5" s="13">
         <f>U5-W5-X5-Z5-AB5</f>
-        <v>15722</v>
+        <v>15719</v>
       </c>
       <c r="AF5" s="14"/>
     </row>
@@ -17281,10 +17282,11 @@
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G6" s="7">
-        <v>27</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
@@ -17297,30 +17299,30 @@
       </c>
       <c r="L6" s="8">
         <f t="shared" si="3"/>
-        <v>566.66666666666663</v>
+        <v>548</v>
       </c>
       <c r="M6" s="8">
-        <f t="shared" si="9"/>
-        <v>190</v>
+        <f t="shared" si="4"/>
+        <v>184</v>
       </c>
       <c r="N6" s="16">
         <f>1000+1000+1500+700+1500</f>
         <v>5700</v>
       </c>
       <c r="O6" s="13">
-        <f t="shared" si="4"/>
-        <v>15299.999999999998</v>
+        <f t="shared" si="5"/>
+        <v>13700</v>
       </c>
       <c r="P6" s="13">
         <f>O6*1</f>
-        <v>15299.999999999998</v>
+        <v>13700</v>
       </c>
       <c r="Q6" s="13">
         <v>0</v>
       </c>
       <c r="R6" s="13">
-        <f>(1000+1000+1500+700+1500)/30*F6</f>
-        <v>5130</v>
+        <f>(1000+1000+1500+700+1500)/31*F6</f>
+        <v>4596.7741935483873</v>
       </c>
       <c r="S6" s="16">
         <f t="shared" si="0"/>
@@ -17329,7 +17331,7 @@
       <c r="T6" s="13"/>
       <c r="U6" s="13">
         <f t="shared" si="1"/>
-        <v>20430</v>
+        <v>18296.774193548386</v>
       </c>
       <c r="V6" s="8">
         <v>0</v>
@@ -17340,14 +17342,14 @@
       </c>
       <c r="X6" s="8">
         <f>IF(O6&lt;=21000,ROUNDUP(O6*0.75%,0),0)</f>
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="Y6" s="13">
-        <f t="shared" si="7"/>
-        <v>20315</v>
+        <f t="shared" si="8"/>
+        <v>18193.774193548386</v>
       </c>
       <c r="Z6" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>130</v>
       </c>
       <c r="AA6" s="17">
@@ -17359,7 +17361,7 @@
       <c r="AD6" s="18"/>
       <c r="AE6" s="13">
         <f>U6-W6-X6-Z6-AB6</f>
-        <v>20185</v>
+        <v>18063.774193548386</v>
       </c>
       <c r="AF6" s="14"/>
     </row>
@@ -17378,7 +17380,7 @@
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G7" s="7">
         <f t="shared" si="2"/>
@@ -17395,30 +17397,30 @@
       </c>
       <c r="L7" s="8">
         <f t="shared" si="3"/>
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="M7" s="8">
-        <f t="shared" si="9"/>
-        <v>143.33333333333334</v>
+        <f t="shared" si="4"/>
+        <v>139</v>
       </c>
       <c r="N7" s="9">
         <f>2800+1500</f>
         <v>4300</v>
       </c>
       <c r="O7" s="8">
-        <f t="shared" si="4"/>
-        <v>10200</v>
+        <f t="shared" si="5"/>
+        <v>10199</v>
       </c>
       <c r="P7" s="8">
         <f t="shared" ref="P7:P40" si="11">O7*0.7</f>
-        <v>7140</v>
+        <v>7139.2999999999993</v>
       </c>
       <c r="Q7" s="13">
         <f>O7*0.3</f>
-        <v>3060</v>
+        <v>3059.7</v>
       </c>
       <c r="R7" s="8">
-        <f>(800+1000+1000+1500)/30*F7</f>
+        <f>(800+1000+1000+1500)/31*F7</f>
         <v>4300</v>
       </c>
       <c r="S7" s="9">
@@ -17428,26 +17430,26 @@
       <c r="T7" s="8"/>
       <c r="U7" s="8">
         <f t="shared" si="1"/>
-        <v>14500</v>
+        <v>14499</v>
       </c>
       <c r="V7" s="8">
         <f>P7</f>
-        <v>7140</v>
+        <v>7139.2999999999993</v>
       </c>
       <c r="W7" s="8">
         <f t="shared" ref="W7:W38" si="12">ROUND(IF(V7&lt;=15000,V7*12%,IF(V7&gt;15000,0)),0)</f>
         <v>857</v>
       </c>
       <c r="X7" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>77</v>
       </c>
       <c r="Y7" s="8">
-        <f t="shared" si="7"/>
-        <v>13566</v>
+        <f t="shared" si="8"/>
+        <v>13565</v>
       </c>
       <c r="Z7" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>110</v>
       </c>
       <c r="AA7" s="17">
@@ -17458,7 +17460,7 @@
       <c r="AD7" s="8"/>
       <c r="AE7" s="13">
         <f>(U7-W7-X7-Z7-AB7)</f>
-        <v>13456</v>
+        <v>13455</v>
       </c>
       <c r="AF7" s="14"/>
     </row>
@@ -17477,10 +17479,11 @@
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6">
-        <v>16</v>
-      </c>
-      <c r="G8" s="6">
-        <v>16</v>
+        <v>31</v>
+      </c>
+      <c r="G8" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -17490,31 +17493,31 @@
       <c r="K8" s="6">
         <v>15500</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="8">
         <f t="shared" si="3"/>
-        <v>516.66666666666663</v>
-      </c>
-      <c r="M8" s="13">
-        <f t="shared" si="9"/>
-        <v>193.33333333333334</v>
+        <v>500</v>
+      </c>
+      <c r="M8" s="8">
+        <f t="shared" si="4"/>
+        <v>187</v>
       </c>
       <c r="N8" s="16">
         <v>5800</v>
       </c>
       <c r="O8" s="13">
-        <f t="shared" si="4"/>
-        <v>8266.6666666666661</v>
+        <f t="shared" si="5"/>
+        <v>15500</v>
       </c>
       <c r="P8" s="13">
         <f>O8*1</f>
-        <v>8266.6666666666661</v>
+        <v>15500</v>
       </c>
       <c r="Q8" s="82" t="s">
         <v>54</v>
       </c>
       <c r="R8" s="13">
-        <f>(11500)/30*F8</f>
-        <v>6133.333333333333</v>
+        <f>(11500)/31*F8</f>
+        <v>11500</v>
       </c>
       <c r="S8" s="16">
         <f t="shared" si="0"/>
@@ -17523,7 +17526,7 @@
       <c r="T8" s="13"/>
       <c r="U8" s="13">
         <f>P8+S8+R8+T8</f>
-        <v>14400</v>
+        <v>27000</v>
       </c>
       <c r="V8" s="13">
         <v>0</v>
@@ -17533,16 +17536,16 @@
         <v>0</v>
       </c>
       <c r="X8" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y8" s="13">
-        <f t="shared" si="7"/>
-        <v>14400</v>
+        <f t="shared" si="8"/>
+        <v>27000</v>
       </c>
       <c r="Z8" s="11">
-        <f t="shared" si="8"/>
-        <v>110</v>
+        <f t="shared" si="9"/>
+        <v>150</v>
       </c>
       <c r="AA8" s="17">
         <v>110</v>
@@ -17552,7 +17555,7 @@
       <c r="AD8" s="13"/>
       <c r="AE8" s="13">
         <f>(U8-W8-X8-Z8-AB8)</f>
-        <v>14290</v>
+        <v>26850</v>
       </c>
       <c r="AF8" s="14"/>
     </row>
@@ -17571,11 +17574,11 @@
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G9" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
@@ -17588,31 +17591,31 @@
       </c>
       <c r="L9" s="8">
         <f t="shared" si="3"/>
-        <v>933.33333333333337</v>
+        <v>903</v>
       </c>
       <c r="M9" s="8">
-        <f t="shared" si="9"/>
-        <v>133.33333333333334</v>
+        <f t="shared" si="4"/>
+        <v>129</v>
       </c>
       <c r="N9" s="16">
         <f>2000+2000</f>
         <v>4000</v>
       </c>
       <c r="O9" s="13">
-        <f t="shared" si="4"/>
-        <v>28000</v>
+        <f t="shared" si="5"/>
+        <v>26187</v>
       </c>
       <c r="P9" s="13">
         <f>O9*1</f>
-        <v>28000</v>
+        <v>26187</v>
       </c>
       <c r="Q9" s="13">
         <f>O9*0</f>
         <v>0</v>
       </c>
       <c r="R9" s="8">
-        <f>(2000+2000)/30*F9</f>
-        <v>4000.0000000000005</v>
+        <f>(2000+2000)/31*F9</f>
+        <v>3741.9354838709678</v>
       </c>
       <c r="S9" s="16">
         <f t="shared" si="0"/>
@@ -17621,7 +17624,7 @@
       <c r="T9" s="13"/>
       <c r="U9" s="8">
         <f t="shared" si="1"/>
-        <v>32000</v>
+        <v>29928.93548387097</v>
       </c>
       <c r="V9" s="13">
         <v>0</v>
@@ -17631,15 +17634,15 @@
         <v>0</v>
       </c>
       <c r="X9" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y9" s="8">
-        <f t="shared" si="7"/>
-        <v>32000</v>
+        <f t="shared" si="8"/>
+        <v>29928.93548387097</v>
       </c>
       <c r="Z9" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>150</v>
       </c>
       <c r="AA9" s="17">
@@ -17650,7 +17653,7 @@
       <c r="AD9" s="13"/>
       <c r="AE9" s="13">
         <f>U9-W9-X9-Z9-AB9-AC9</f>
-        <v>31850</v>
+        <v>29778.93548387097</v>
       </c>
       <c r="AF9" s="14"/>
     </row>
@@ -17669,13 +17672,15 @@
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="7">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G10" s="7">
         <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="H10" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="H10" s="6">
+        <v>1</v>
+      </c>
       <c r="I10" s="6"/>
       <c r="J10" s="6">
         <v>15500</v>
@@ -17685,11 +17690,11 @@
       </c>
       <c r="L10" s="8">
         <f t="shared" si="3"/>
-        <v>366.66666666666669</v>
+        <v>355</v>
       </c>
       <c r="M10" s="8">
-        <f t="shared" si="9"/>
-        <v>150</v>
+        <f t="shared" si="4"/>
+        <v>145</v>
       </c>
       <c r="N10" s="16">
         <f>3000+1000+500</f>
@@ -17697,48 +17702,48 @@
       </c>
       <c r="O10" s="13">
         <f>L10*F10</f>
-        <v>6600</v>
+        <v>10650</v>
       </c>
       <c r="P10" s="13">
         <f t="shared" ref="P10" si="13">O10*0.7</f>
-        <v>4620</v>
+        <v>7454.9999999999991</v>
       </c>
       <c r="Q10" s="13">
         <f t="shared" ref="Q10:Q38" si="14">O10*0.3</f>
-        <v>1980</v>
+        <v>3195</v>
       </c>
       <c r="R10" s="8">
-        <f>(3000+1000+500)/30*F10</f>
-        <v>2700</v>
+        <f>(3000+1000+500)/31*F10</f>
+        <v>4354.8387096774195</v>
       </c>
       <c r="S10" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="T10" s="13"/>
       <c r="U10" s="8">
         <f t="shared" si="1"/>
-        <v>9300</v>
+        <v>15504.83870967742</v>
       </c>
       <c r="V10" s="13">
         <f t="shared" ref="V10:V37" si="15">P10</f>
-        <v>4620</v>
+        <v>7454.9999999999991</v>
       </c>
       <c r="W10" s="13">
         <f t="shared" si="12"/>
-        <v>554</v>
+        <v>895</v>
       </c>
       <c r="X10" s="8">
-        <f t="shared" si="6"/>
-        <v>50</v>
+        <f t="shared" si="7"/>
+        <v>80</v>
       </c>
       <c r="Y10" s="8">
-        <f t="shared" si="7"/>
-        <v>8696</v>
+        <f t="shared" si="8"/>
+        <v>14529.83870967742</v>
       </c>
       <c r="Z10" s="11">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>130</v>
       </c>
       <c r="AA10" s="17">
         <v>130</v>
@@ -17748,7 +17753,7 @@
       <c r="AD10" s="13"/>
       <c r="AE10" s="13">
         <f t="shared" ref="AE10:AE16" si="16">U10-W10-X10-Z10-AB10</f>
-        <v>8696</v>
+        <v>14399.83870967742</v>
       </c>
       <c r="AF10" s="14"/>
     </row>
@@ -17757,7 +17762,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>45</v>
@@ -17766,16 +17771,12 @@
         <v>46</v>
       </c>
       <c r="E11" s="20"/>
-      <c r="F11" s="20">
-        <v>30</v>
-      </c>
+      <c r="F11" s="20"/>
       <c r="G11" s="20">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="20">
-        <v>1</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="H11" s="20"/>
       <c r="I11" s="20"/>
       <c r="J11" s="20">
         <v>19000</v>
@@ -17786,11 +17787,11 @@
       </c>
       <c r="L11" s="21">
         <f t="shared" si="3"/>
-        <v>523.33333333333337</v>
+        <v>506</v>
       </c>
       <c r="M11" s="21">
-        <f t="shared" si="9"/>
-        <v>110</v>
+        <f t="shared" si="4"/>
+        <v>106</v>
       </c>
       <c r="N11" s="22">
         <f>1000+1300+1000</f>
@@ -17798,48 +17799,48 @@
       </c>
       <c r="O11" s="21">
         <f>L11*F11</f>
-        <v>15700.000000000002</v>
+        <v>0</v>
       </c>
       <c r="P11" s="21">
         <f t="shared" si="11"/>
-        <v>10990</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="21">
         <f t="shared" si="14"/>
-        <v>4710</v>
+        <v>0</v>
       </c>
       <c r="R11" s="21">
-        <f>(1000+1300+1000)/30*F11</f>
-        <v>3300</v>
+        <f>(1000+1300+1000)/31*F11</f>
+        <v>0</v>
       </c>
       <c r="S11" s="22">
         <f t="shared" si="0"/>
-        <v>633.33333333333337</v>
+        <v>0</v>
       </c>
       <c r="T11" s="21"/>
       <c r="U11" s="21">
         <f t="shared" si="1"/>
-        <v>19633.333333333336</v>
+        <v>0</v>
       </c>
       <c r="V11" s="21">
         <f t="shared" si="15"/>
-        <v>10990</v>
+        <v>0</v>
       </c>
       <c r="W11" s="21">
         <f t="shared" si="12"/>
-        <v>1319</v>
+        <v>0</v>
       </c>
       <c r="X11" s="21">
-        <f t="shared" si="6"/>
-        <v>118</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="Y11" s="21">
-        <f t="shared" si="7"/>
-        <v>18196.333333333336</v>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="Z11" s="23">
-        <f t="shared" si="8"/>
-        <v>130</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="AA11" s="24">
         <v>130</v>
@@ -17851,11 +17852,11 @@
       <c r="AD11" s="21"/>
       <c r="AE11" s="21">
         <f t="shared" si="16"/>
-        <v>16566.333333333336</v>
+        <v>-1500</v>
       </c>
       <c r="AF11" s="70">
         <f>AE11-700</f>
-        <v>15866.333333333336</v>
+        <v>-2200</v>
       </c>
     </row>
     <row r="12" spans="1:34" s="42" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -17863,7 +17864,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="19">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>47</v>
@@ -17871,7 +17872,7 @@
       <c r="D12" s="20"/>
       <c r="E12" s="20"/>
       <c r="F12" s="20">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G12" s="20">
         <f t="shared" si="2"/>
@@ -17888,11 +17889,11 @@
       </c>
       <c r="L12" s="21">
         <f t="shared" si="3"/>
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="M12" s="21">
-        <f t="shared" si="9"/>
-        <v>33.333333333333336</v>
+        <f t="shared" si="4"/>
+        <v>32</v>
       </c>
       <c r="N12" s="22">
         <f>500+500</f>
@@ -17900,19 +17901,19 @@
       </c>
       <c r="O12" s="21">
         <f>L12*F12</f>
-        <v>5800</v>
+        <v>5820</v>
       </c>
       <c r="P12" s="21">
         <f t="shared" si="11"/>
-        <v>4059.9999999999995</v>
+        <v>4073.9999999999995</v>
       </c>
       <c r="Q12" s="21">
         <f t="shared" si="14"/>
-        <v>1740</v>
+        <v>1746</v>
       </c>
       <c r="R12" s="21">
-        <f>(500+500)/30*F12</f>
-        <v>966.66666666666674</v>
+        <f>(500+500)/31*F12</f>
+        <v>967.74193548387098</v>
       </c>
       <c r="S12" s="22">
         <f t="shared" si="0"/>
@@ -17921,26 +17922,26 @@
       <c r="T12" s="21"/>
       <c r="U12" s="21">
         <f t="shared" si="1"/>
-        <v>6766.666666666667</v>
+        <v>6787.7419354838712</v>
       </c>
       <c r="V12" s="21">
         <f t="shared" si="15"/>
-        <v>4059.9999999999995</v>
+        <v>4073.9999999999995</v>
       </c>
       <c r="W12" s="21">
         <f t="shared" si="12"/>
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="X12" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>44</v>
       </c>
       <c r="Y12" s="21">
-        <f t="shared" si="7"/>
-        <v>6235.666666666667</v>
+        <f t="shared" si="8"/>
+        <v>6254.7419354838712</v>
       </c>
       <c r="Z12" s="23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA12" s="24">
@@ -17954,7 +17955,7 @@
       <c r="AD12" s="21"/>
       <c r="AE12" s="21">
         <f t="shared" si="16"/>
-        <v>5735.666666666667</v>
+        <v>5754.7419354838712</v>
       </c>
       <c r="AF12" s="71"/>
     </row>
@@ -17963,7 +17964,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>48</v>
@@ -17975,7 +17976,7 @@
       </c>
       <c r="G13" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="27" t="s">
@@ -18025,15 +18026,15 @@
         <v>726</v>
       </c>
       <c r="X13" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>65</v>
       </c>
       <c r="Y13" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8794</v>
       </c>
       <c r="Z13" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA13" s="17"/>
@@ -18053,7 +18054,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="28">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" s="29" t="s">
         <v>50</v>
@@ -18063,11 +18064,11 @@
       </c>
       <c r="E14" s="29"/>
       <c r="F14" s="7">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G14" s="7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H14" s="29"/>
       <c r="I14" s="29"/>
@@ -18078,12 +18079,12 @@
         <f>6500</f>
         <v>6500</v>
       </c>
-      <c r="L14" s="30">
-        <f>K14/30</f>
-        <v>216.66666666666666</v>
-      </c>
-      <c r="M14" s="30">
-        <f>N14/30</f>
+      <c r="L14" s="8">
+        <f t="shared" si="3"/>
+        <v>210</v>
+      </c>
+      <c r="M14" s="8">
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="N14" s="31">
@@ -18091,19 +18092,19 @@
       </c>
       <c r="O14" s="30">
         <f t="shared" si="17"/>
-        <v>6066.6666666666661</v>
+        <v>4200</v>
       </c>
       <c r="P14" s="30">
         <f t="shared" si="11"/>
-        <v>4246.6666666666661</v>
+        <v>2940</v>
       </c>
       <c r="Q14" s="30">
         <f t="shared" si="14"/>
-        <v>1819.9999999999998</v>
+        <v>1260</v>
       </c>
       <c r="R14" s="30">
-        <f>300/30*F14</f>
-        <v>280</v>
+        <f>300/31*F14</f>
+        <v>193.54838709677421</v>
       </c>
       <c r="S14" s="31">
         <f t="shared" si="0"/>
@@ -18112,26 +18113,26 @@
       <c r="T14" s="30"/>
       <c r="U14" s="8">
         <f t="shared" si="1"/>
-        <v>6346.6666666666661</v>
+        <v>4393.5483870967746</v>
       </c>
       <c r="V14" s="30">
         <f t="shared" si="15"/>
-        <v>4246.6666666666661</v>
+        <v>2940</v>
       </c>
       <c r="W14" s="30">
         <f t="shared" si="12"/>
-        <v>510</v>
+        <v>353</v>
       </c>
       <c r="X14" s="8">
-        <f t="shared" si="6"/>
-        <v>46</v>
+        <f t="shared" si="7"/>
+        <v>32</v>
       </c>
       <c r="Y14" s="8">
-        <f t="shared" si="7"/>
-        <v>5790.6666666666661</v>
+        <f t="shared" si="8"/>
+        <v>4008.5483870967746</v>
       </c>
       <c r="Z14" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA14" s="32">
@@ -18143,7 +18144,7 @@
       <c r="AD14" s="30"/>
       <c r="AE14" s="30">
         <f t="shared" si="16"/>
-        <v>5790.6666666666661</v>
+        <v>4008.5483870967746</v>
       </c>
       <c r="AF14" s="14"/>
       <c r="AG14" s="72"/>
@@ -18154,7 +18155,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>52</v>
@@ -18168,7 +18169,7 @@
       </c>
       <c r="G15" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="27" t="s">
@@ -18217,15 +18218,15 @@
         <v>780</v>
       </c>
       <c r="X15" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>70</v>
       </c>
       <c r="Y15" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8865</v>
       </c>
       <c r="Z15" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA15" s="17" t="s">
@@ -18247,7 +18248,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>55</v>
@@ -18257,11 +18258,11 @@
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="7">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G16" s="7">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="27" t="s">
@@ -18278,19 +18279,19 @@
       <c r="N16" s="16"/>
       <c r="O16" s="13">
         <f t="shared" si="17"/>
-        <v>3520</v>
+        <v>8640</v>
       </c>
       <c r="P16" s="13">
         <f t="shared" si="11"/>
-        <v>2464</v>
+        <v>6048</v>
       </c>
       <c r="Q16" s="13">
         <f t="shared" si="14"/>
-        <v>1056</v>
+        <v>2592</v>
       </c>
       <c r="R16" s="13">
         <f>15*F16</f>
-        <v>165</v>
+        <v>405</v>
       </c>
       <c r="S16" s="13">
         <f t="shared" si="18"/>
@@ -18299,26 +18300,26 @@
       <c r="T16" s="13"/>
       <c r="U16" s="8">
         <f t="shared" si="1"/>
-        <v>3685</v>
+        <v>9045</v>
       </c>
       <c r="V16" s="13">
         <f t="shared" si="15"/>
-        <v>2464</v>
+        <v>6048</v>
       </c>
       <c r="W16" s="13">
         <f t="shared" si="12"/>
-        <v>296</v>
+        <v>726</v>
       </c>
       <c r="X16" s="8">
-        <f t="shared" si="6"/>
-        <v>27</v>
+        <f t="shared" si="7"/>
+        <v>65</v>
       </c>
       <c r="Y16" s="8">
-        <f t="shared" si="7"/>
-        <v>3362</v>
+        <f t="shared" si="8"/>
+        <v>8254</v>
       </c>
       <c r="Z16" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA16" s="17" t="s">
@@ -18329,7 +18330,7 @@
       <c r="AD16" s="13"/>
       <c r="AE16" s="13">
         <f t="shared" si="16"/>
-        <v>3362</v>
+        <v>8254</v>
       </c>
       <c r="AF16" s="14"/>
       <c r="AG16" s="72"/>
@@ -18340,7 +18341,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>56</v>
@@ -18348,11 +18349,11 @@
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
       <c r="F17" s="7">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G17" s="7">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="27" t="s">
@@ -18369,19 +18370,19 @@
       <c r="N17" s="16"/>
       <c r="O17" s="13">
         <f t="shared" si="17"/>
-        <v>5120</v>
+        <v>9280</v>
       </c>
       <c r="P17" s="13">
         <f t="shared" si="11"/>
-        <v>3584</v>
+        <v>6496</v>
       </c>
       <c r="Q17" s="13">
         <f t="shared" si="14"/>
-        <v>1536</v>
+        <v>2784</v>
       </c>
       <c r="R17" s="13">
         <f>15*F17</f>
-        <v>240</v>
+        <v>435</v>
       </c>
       <c r="S17" s="13">
         <f t="shared" si="18"/>
@@ -18390,26 +18391,26 @@
       <c r="T17" s="13"/>
       <c r="U17" s="8">
         <f t="shared" si="1"/>
-        <v>5360</v>
+        <v>9715</v>
       </c>
       <c r="V17" s="13">
         <f t="shared" si="15"/>
-        <v>3584</v>
+        <v>6496</v>
       </c>
       <c r="W17" s="13">
         <f t="shared" si="12"/>
-        <v>430</v>
+        <v>780</v>
       </c>
       <c r="X17" s="8">
-        <f t="shared" si="6"/>
-        <v>39</v>
+        <f t="shared" si="7"/>
+        <v>70</v>
       </c>
       <c r="Y17" s="8">
-        <f t="shared" si="7"/>
-        <v>4891</v>
+        <f t="shared" si="8"/>
+        <v>8865</v>
       </c>
       <c r="Z17" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA17" s="17">
@@ -18420,7 +18421,7 @@
       <c r="AD17" s="13"/>
       <c r="AE17" s="30">
         <f>U17-W17-X17-Z17-AB17-AC17</f>
-        <v>4891</v>
+        <v>8865</v>
       </c>
       <c r="AF17" s="14"/>
       <c r="AG17" s="72"/>
@@ -18431,7 +18432,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>57</v>
@@ -18439,9 +18440,9 @@
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
       <c r="F18" s="6">
-        <v>27</v>
-      </c>
-      <c r="G18" s="6">
+        <v>28</v>
+      </c>
+      <c r="G18" s="7">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
@@ -18461,47 +18462,47 @@
       <c r="N18" s="16"/>
       <c r="O18" s="13">
         <f t="shared" si="17"/>
-        <v>8640</v>
+        <v>8960</v>
       </c>
       <c r="P18" s="13">
         <f t="shared" si="11"/>
-        <v>6048</v>
+        <v>6272</v>
       </c>
       <c r="Q18" s="13">
         <f t="shared" si="14"/>
-        <v>2592</v>
+        <v>2688</v>
       </c>
       <c r="R18" s="13">
         <f>(65+15)*F18</f>
-        <v>2160</v>
+        <v>2240</v>
       </c>
       <c r="S18" s="13">
-        <f>H18*(L18+M18)+615</f>
-        <v>615</v>
+        <f>H18*(L18+M18)</f>
+        <v>0</v>
       </c>
       <c r="T18" s="13"/>
       <c r="U18" s="13">
         <f t="shared" si="1"/>
-        <v>11415</v>
+        <v>11200</v>
       </c>
       <c r="V18" s="13">
         <f t="shared" si="15"/>
-        <v>6048</v>
+        <v>6272</v>
       </c>
       <c r="W18" s="13">
         <f t="shared" si="12"/>
-        <v>726</v>
+        <v>753</v>
       </c>
       <c r="X18" s="13">
-        <f t="shared" si="6"/>
-        <v>65</v>
+        <f t="shared" si="7"/>
+        <v>68</v>
       </c>
       <c r="Y18" s="13">
-        <f t="shared" si="7"/>
-        <v>10624</v>
+        <f t="shared" si="8"/>
+        <v>10379</v>
       </c>
       <c r="Z18" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>110</v>
       </c>
       <c r="AA18" s="17">
@@ -18513,11 +18514,9 @@
       <c r="AD18" s="13"/>
       <c r="AE18" s="13">
         <f>U18-W18-X18-Z18-AB18</f>
-        <v>10514</v>
-      </c>
-      <c r="AF18" s="14">
-        <v>9497</v>
-      </c>
+        <v>10269</v>
+      </c>
+      <c r="AF18" s="14"/>
       <c r="AG18" s="77"/>
       <c r="AH18" s="74"/>
     </row>
@@ -18526,7 +18525,7 @@
         <v>21</v>
       </c>
       <c r="B19" s="15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" s="33" t="s">
         <v>59</v>
@@ -18534,11 +18533,11 @@
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G19" s="7">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="27" t="s">
@@ -18555,19 +18554,19 @@
       <c r="N19" s="16"/>
       <c r="O19" s="13">
         <f t="shared" si="17"/>
-        <v>8320</v>
+        <v>8960</v>
       </c>
       <c r="P19" s="13">
         <f t="shared" si="11"/>
-        <v>5824</v>
+        <v>6272</v>
       </c>
       <c r="Q19" s="13">
         <f t="shared" si="14"/>
-        <v>2496</v>
+        <v>2688</v>
       </c>
       <c r="R19" s="13">
         <f>15*F19</f>
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="S19" s="13">
         <f t="shared" si="18"/>
@@ -18576,26 +18575,26 @@
       <c r="T19" s="13"/>
       <c r="U19" s="8">
         <f t="shared" si="1"/>
-        <v>8710</v>
+        <v>9380</v>
       </c>
       <c r="V19" s="13">
         <f t="shared" si="15"/>
-        <v>5824</v>
+        <v>6272</v>
       </c>
       <c r="W19" s="13">
         <f t="shared" si="12"/>
-        <v>699</v>
+        <v>753</v>
       </c>
       <c r="X19" s="8">
-        <f t="shared" si="6"/>
-        <v>63</v>
+        <f t="shared" si="7"/>
+        <v>68</v>
       </c>
       <c r="Y19" s="8">
-        <f t="shared" si="7"/>
-        <v>7948</v>
+        <f t="shared" si="8"/>
+        <v>8559</v>
       </c>
       <c r="Z19" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA19" s="17"/>
@@ -18604,7 +18603,7 @@
       <c r="AD19" s="13"/>
       <c r="AE19" s="13">
         <f>U19-W19-X19-Z19-AB19-AC19</f>
-        <v>7948</v>
+        <v>8559</v>
       </c>
       <c r="AF19" s="14"/>
       <c r="AG19" s="72"/>
@@ -18615,7 +18614,7 @@
         <v>22</v>
       </c>
       <c r="B20" s="28">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" s="29" t="s">
         <v>60</v>
@@ -18625,15 +18624,13 @@
       </c>
       <c r="E20" s="29"/>
       <c r="F20" s="6">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G20" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="H20" s="29">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H20" s="29"/>
       <c r="I20" s="34" t="s">
         <v>49</v>
       </c>
@@ -18648,47 +18645,47 @@
       <c r="N20" s="31"/>
       <c r="O20" s="30">
         <f>L20*F20</f>
-        <v>5940</v>
+        <v>6820</v>
       </c>
       <c r="P20" s="30">
         <f t="shared" si="11"/>
-        <v>4158</v>
+        <v>4774</v>
       </c>
       <c r="Q20" s="30">
         <f t="shared" si="14"/>
-        <v>1782</v>
+        <v>2046</v>
       </c>
       <c r="R20" s="30">
         <f>10*F20</f>
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="S20" s="30">
         <f t="shared" si="18"/>
-        <v>690</v>
+        <v>0</v>
       </c>
       <c r="T20" s="30"/>
       <c r="U20" s="13">
         <f t="shared" si="1"/>
-        <v>6900</v>
+        <v>7130</v>
       </c>
       <c r="V20" s="30">
         <f t="shared" si="15"/>
-        <v>4158</v>
+        <v>4774</v>
       </c>
       <c r="W20" s="30">
         <f t="shared" si="12"/>
-        <v>499</v>
+        <v>573</v>
       </c>
       <c r="X20" s="13">
-        <f t="shared" si="6"/>
-        <v>45</v>
+        <f t="shared" si="7"/>
+        <v>52</v>
       </c>
       <c r="Y20" s="13">
-        <f t="shared" si="7"/>
-        <v>6356</v>
+        <f t="shared" si="8"/>
+        <v>6505</v>
       </c>
       <c r="Z20" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA20" s="32"/>
@@ -18697,7 +18694,7 @@
       <c r="AD20" s="30"/>
       <c r="AE20" s="30">
         <f t="shared" ref="AE20:AE39" si="19">U20-W20-X20-Z20-AB20</f>
-        <v>6356</v>
+        <v>6505</v>
       </c>
       <c r="AF20" s="14"/>
       <c r="AG20" s="77"/>
@@ -18708,7 +18705,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="15">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" s="36" t="s">
         <v>61</v>
@@ -18718,15 +18715,13 @@
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G21" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="H21" s="6">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H21" s="6"/>
       <c r="I21" s="27" t="s">
         <v>58</v>
       </c>
@@ -18740,48 +18735,48 @@
       </c>
       <c r="N21" s="16"/>
       <c r="O21" s="13">
-        <f t="shared" si="4"/>
-        <v>6380</v>
+        <f t="shared" si="5"/>
+        <v>6820</v>
       </c>
       <c r="P21" s="13">
         <f t="shared" si="11"/>
-        <v>4466</v>
+        <v>4774</v>
       </c>
       <c r="Q21" s="13">
         <f t="shared" si="14"/>
-        <v>1914</v>
+        <v>2046</v>
       </c>
       <c r="R21" s="13">
         <f>10*F21</f>
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="S21" s="13">
         <f t="shared" si="18"/>
-        <v>1150</v>
+        <v>0</v>
       </c>
       <c r="T21" s="13"/>
       <c r="U21" s="13">
         <f t="shared" si="1"/>
-        <v>7820</v>
+        <v>7130</v>
       </c>
       <c r="V21" s="13">
         <f t="shared" si="15"/>
-        <v>4466</v>
+        <v>4774</v>
       </c>
       <c r="W21" s="13">
         <f t="shared" si="12"/>
-        <v>536</v>
+        <v>573</v>
       </c>
       <c r="X21" s="13">
-        <f t="shared" si="6"/>
-        <v>48</v>
+        <f t="shared" si="7"/>
+        <v>52</v>
       </c>
       <c r="Y21" s="13">
-        <f t="shared" si="7"/>
-        <v>7236</v>
+        <f t="shared" si="8"/>
+        <v>6505</v>
       </c>
       <c r="Z21" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA21" s="17">
@@ -18792,7 +18787,7 @@
       <c r="AD21" s="13"/>
       <c r="AE21" s="13">
         <f t="shared" si="19"/>
-        <v>7236</v>
+        <v>6505</v>
       </c>
       <c r="AF21" s="14"/>
       <c r="AG21" s="77"/>
@@ -18803,7 +18798,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>62</v>
@@ -18811,11 +18806,11 @@
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G22" s="7">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="27" t="s">
@@ -18832,20 +18827,20 @@
       </c>
       <c r="N22" s="16"/>
       <c r="O22" s="13">
-        <f t="shared" si="4"/>
-        <v>5025</v>
+        <f t="shared" si="5"/>
+        <v>10050</v>
       </c>
       <c r="P22" s="13">
         <f t="shared" si="11"/>
-        <v>3517.5</v>
+        <v>7035</v>
       </c>
       <c r="Q22" s="13">
         <f t="shared" si="14"/>
-        <v>1507.5</v>
+        <v>3015</v>
       </c>
       <c r="R22" s="13">
         <f>M22*F22</f>
-        <v>975</v>
+        <v>1950</v>
       </c>
       <c r="S22" s="13">
         <f t="shared" si="18"/>
@@ -18854,27 +18849,27 @@
       <c r="T22" s="13"/>
       <c r="U22" s="13">
         <f t="shared" si="1"/>
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="V22" s="13">
         <f t="shared" si="15"/>
-        <v>3517.5</v>
+        <v>7035</v>
       </c>
       <c r="W22" s="13">
         <f t="shared" si="12"/>
-        <v>422</v>
+        <v>844</v>
       </c>
       <c r="X22" s="13">
-        <f t="shared" si="6"/>
-        <v>38</v>
+        <f t="shared" si="7"/>
+        <v>76</v>
       </c>
       <c r="Y22" s="13">
-        <f t="shared" si="7"/>
-        <v>5540</v>
+        <f t="shared" si="8"/>
+        <v>11080</v>
       </c>
       <c r="Z22" s="11">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>110</v>
       </c>
       <c r="AA22" s="17"/>
       <c r="AB22" s="13"/>
@@ -18882,7 +18877,7 @@
       <c r="AD22" s="13"/>
       <c r="AE22" s="13">
         <f>U22-W22-X22-Z22-AB22-AC22</f>
-        <v>5540</v>
+        <v>10970</v>
       </c>
       <c r="AF22" s="14"/>
       <c r="AG22" s="77"/>
@@ -18893,7 +18888,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>63</v>
@@ -18907,7 +18902,7 @@
       </c>
       <c r="G23" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="27" t="s">
@@ -18924,7 +18919,7 @@
       </c>
       <c r="N23" s="16"/>
       <c r="O23" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9045</v>
       </c>
       <c r="P23" s="13">
@@ -18957,15 +18952,15 @@
         <v>760</v>
       </c>
       <c r="X23" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>68</v>
       </c>
       <c r="Y23" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9972</v>
       </c>
       <c r="Z23" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>110</v>
       </c>
       <c r="AA23" s="17">
@@ -18987,7 +18982,7 @@
         <v>26</v>
       </c>
       <c r="B24" s="15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>64</v>
@@ -18997,7 +18992,7 @@
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G24" s="7">
         <f t="shared" si="2"/>
@@ -19019,19 +19014,19 @@
       <c r="N24" s="16"/>
       <c r="O24" s="13">
         <f>L24*F24</f>
-        <v>8375</v>
+        <v>8710</v>
       </c>
       <c r="P24" s="13">
         <f t="shared" si="11"/>
-        <v>5862.5</v>
+        <v>6097</v>
       </c>
       <c r="Q24" s="13">
         <f t="shared" si="14"/>
-        <v>2512.5</v>
+        <v>2613</v>
       </c>
       <c r="R24" s="13">
         <f t="shared" ref="R24:R37" si="20">M24*F24</f>
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="S24" s="13">
         <f t="shared" si="18"/>
@@ -19040,38 +19035,38 @@
       <c r="T24" s="13"/>
       <c r="U24" s="8">
         <f t="shared" si="1"/>
-        <v>9625</v>
+        <v>10010</v>
       </c>
       <c r="V24" s="13">
         <f t="shared" si="15"/>
-        <v>5862.5</v>
+        <v>6097</v>
       </c>
       <c r="W24" s="13">
         <f t="shared" si="12"/>
-        <v>704</v>
+        <v>732</v>
       </c>
       <c r="X24" s="8">
-        <f t="shared" si="6"/>
-        <v>63</v>
+        <f t="shared" si="7"/>
+        <v>66</v>
       </c>
       <c r="Y24" s="8">
-        <f t="shared" si="7"/>
-        <v>8858</v>
+        <f t="shared" si="8"/>
+        <v>9212</v>
       </c>
       <c r="Z24" s="11">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>110</v>
       </c>
       <c r="AA24" s="17">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB24" s="13"/>
       <c r="AC24" s="13"/>
       <c r="AD24" s="13"/>
       <c r="AE24" s="13">
         <f t="shared" si="19"/>
-        <v>8858</v>
+        <v>9102</v>
       </c>
       <c r="AF24" s="26"/>
       <c r="AG24" s="72"/>
@@ -19082,7 +19077,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="15">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>66</v>
@@ -19094,9 +19089,9 @@
       <c r="F25" s="6">
         <v>29</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="6"/>
       <c r="I25" s="27" t="s">
@@ -19146,15 +19141,15 @@
         <v>792</v>
       </c>
       <c r="X25" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>71</v>
       </c>
       <c r="Y25" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>10737</v>
       </c>
       <c r="Z25" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>110</v>
       </c>
       <c r="AA25" s="17">
@@ -19176,7 +19171,7 @@
         <v>28</v>
       </c>
       <c r="B26" s="15">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>67</v>
@@ -19190,7 +19185,7 @@
       </c>
       <c r="G26" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="6"/>
       <c r="I26" s="27" t="s">
@@ -19240,15 +19235,15 @@
         <v>816</v>
       </c>
       <c r="X26" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>73</v>
       </c>
       <c r="Y26" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>10711</v>
       </c>
       <c r="Z26" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>110</v>
       </c>
       <c r="AA26" s="17">
@@ -19270,7 +19265,7 @@
         <v>29</v>
       </c>
       <c r="B27" s="15">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>68</v>
@@ -19284,7 +19279,7 @@
       </c>
       <c r="G27" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="27" t="s">
@@ -19334,15 +19329,15 @@
         <v>737</v>
       </c>
       <c r="X27" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>66</v>
       </c>
       <c r="Y27" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9997</v>
       </c>
       <c r="Z27" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>110</v>
       </c>
       <c r="AA27" s="17">
@@ -19365,7 +19360,7 @@
         <v>30</v>
       </c>
       <c r="B28" s="15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>69</v>
@@ -19379,11 +19374,9 @@
       </c>
       <c r="G28" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H28" s="6">
         <v>1</v>
       </c>
+      <c r="H28" s="6"/>
       <c r="I28" s="27" t="s">
         <v>58</v>
       </c>
@@ -19415,12 +19408,12 @@
       </c>
       <c r="S28" s="13">
         <f t="shared" si="18"/>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T28" s="13"/>
       <c r="U28" s="8">
         <f t="shared" si="1"/>
-        <v>12400</v>
+        <v>12000</v>
       </c>
       <c r="V28" s="13">
         <f t="shared" si="15"/>
@@ -19431,15 +19424,15 @@
         <v>819</v>
       </c>
       <c r="X28" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>74</v>
       </c>
       <c r="Y28" s="8">
-        <f t="shared" si="7"/>
-        <v>11507</v>
+        <f t="shared" si="8"/>
+        <v>11107</v>
       </c>
       <c r="Z28" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>110</v>
       </c>
       <c r="AA28" s="17">
@@ -19450,7 +19443,7 @@
       <c r="AD28" s="13"/>
       <c r="AE28" s="13">
         <f t="shared" si="19"/>
-        <v>11397</v>
+        <v>10997</v>
       </c>
       <c r="AF28" s="37"/>
       <c r="AG28" s="72"/>
@@ -19461,7 +19454,7 @@
         <v>31</v>
       </c>
       <c r="B29" s="15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>70</v>
@@ -19471,11 +19464,11 @@
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="7">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G29" s="7">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="27" t="s">
@@ -19493,19 +19486,19 @@
       <c r="N29" s="16"/>
       <c r="O29" s="13">
         <f t="shared" si="21"/>
-        <v>8040</v>
+        <v>10385</v>
       </c>
       <c r="P29" s="13">
         <f t="shared" si="22"/>
-        <v>5628</v>
+        <v>7269.4999999999991</v>
       </c>
       <c r="Q29" s="13">
         <f t="shared" si="14"/>
-        <v>2412</v>
+        <v>3115.5</v>
       </c>
       <c r="R29" s="13">
         <f t="shared" si="20"/>
-        <v>1560</v>
+        <v>2015</v>
       </c>
       <c r="S29" s="13">
         <f t="shared" si="18"/>
@@ -19514,39 +19507,37 @@
       <c r="T29" s="13"/>
       <c r="U29" s="8">
         <f t="shared" si="1"/>
-        <v>9600</v>
+        <v>12400</v>
       </c>
       <c r="V29" s="13">
         <f t="shared" si="15"/>
-        <v>5628</v>
+        <v>7269.4999999999991</v>
       </c>
       <c r="W29" s="13">
         <f t="shared" si="12"/>
-        <v>675</v>
+        <v>872</v>
       </c>
       <c r="X29" s="8">
-        <f t="shared" si="6"/>
-        <v>61</v>
+        <f t="shared" si="7"/>
+        <v>78</v>
       </c>
       <c r="Y29" s="8">
-        <f t="shared" si="7"/>
-        <v>8864</v>
+        <f t="shared" si="8"/>
+        <v>11450</v>
       </c>
       <c r="Z29" s="11">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>110</v>
       </c>
       <c r="AA29" s="17">
         <v>110</v>
       </c>
-      <c r="AB29" s="13">
-        <v>2000</v>
-      </c>
+      <c r="AB29" s="13"/>
       <c r="AC29" s="13"/>
       <c r="AD29" s="13"/>
       <c r="AE29" s="13">
         <f t="shared" si="19"/>
-        <v>6864</v>
+        <v>11340</v>
       </c>
       <c r="AF29" s="37"/>
       <c r="AG29" s="72"/>
@@ -19557,7 +19548,7 @@
         <v>32</v>
       </c>
       <c r="B30" s="15">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>71</v>
@@ -19567,7 +19558,7 @@
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G30" s="7">
         <f t="shared" si="2"/>
@@ -19589,19 +19580,19 @@
       <c r="N30" s="16"/>
       <c r="O30" s="13">
         <f t="shared" si="21"/>
-        <v>9750</v>
+        <v>10075</v>
       </c>
       <c r="P30" s="13">
         <f t="shared" si="22"/>
-        <v>6825</v>
+        <v>7052.5</v>
       </c>
       <c r="Q30" s="13">
         <f t="shared" si="14"/>
-        <v>2925</v>
+        <v>3022.5</v>
       </c>
       <c r="R30" s="13">
         <f t="shared" si="20"/>
-        <v>2250</v>
+        <v>2325</v>
       </c>
       <c r="S30" s="13">
         <f t="shared" si="18"/>
@@ -19610,26 +19601,26 @@
       <c r="T30" s="13"/>
       <c r="U30" s="8">
         <f t="shared" si="1"/>
-        <v>12000</v>
+        <v>12400</v>
       </c>
       <c r="V30" s="13">
         <f t="shared" si="15"/>
-        <v>6825</v>
+        <v>7052.5</v>
       </c>
       <c r="W30" s="13">
         <f t="shared" si="12"/>
-        <v>819</v>
+        <v>846</v>
       </c>
       <c r="X30" s="8">
-        <f t="shared" si="6"/>
-        <v>74</v>
+        <f t="shared" si="7"/>
+        <v>76</v>
       </c>
       <c r="Y30" s="8">
-        <f t="shared" si="7"/>
-        <v>11107</v>
+        <f t="shared" si="8"/>
+        <v>11478</v>
       </c>
       <c r="Z30" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>110</v>
       </c>
       <c r="AA30" s="17">
@@ -19640,7 +19631,7 @@
       <c r="AD30" s="13"/>
       <c r="AE30" s="13">
         <f t="shared" si="19"/>
-        <v>10997</v>
+        <v>11368</v>
       </c>
       <c r="AF30" s="37"/>
       <c r="AG30" s="72"/>
@@ -19651,7 +19642,7 @@
         <v>34</v>
       </c>
       <c r="B31" s="15">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>72</v>
@@ -19661,11 +19652,11 @@
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="7">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G31" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="27" t="s">
@@ -19683,19 +19674,19 @@
       <c r="N31" s="16"/>
       <c r="O31" s="13">
         <f t="shared" si="21"/>
-        <v>8775</v>
+        <v>9750</v>
       </c>
       <c r="P31" s="13">
         <f t="shared" si="22"/>
-        <v>6142.5</v>
+        <v>6825</v>
       </c>
       <c r="Q31" s="13">
         <f t="shared" si="14"/>
-        <v>2632.5</v>
+        <v>2925</v>
       </c>
       <c r="R31" s="13">
         <f t="shared" si="20"/>
-        <v>2025</v>
+        <v>2250</v>
       </c>
       <c r="S31" s="13">
         <f t="shared" si="18"/>
@@ -19704,26 +19695,26 @@
       <c r="T31" s="13"/>
       <c r="U31" s="8">
         <f t="shared" si="1"/>
-        <v>10800</v>
+        <v>12000</v>
       </c>
       <c r="V31" s="13">
         <f t="shared" si="15"/>
-        <v>6142.5</v>
+        <v>6825</v>
       </c>
       <c r="W31" s="13">
         <f t="shared" si="12"/>
-        <v>737</v>
+        <v>819</v>
       </c>
       <c r="X31" s="8">
-        <f t="shared" si="6"/>
-        <v>66</v>
+        <f t="shared" si="7"/>
+        <v>74</v>
       </c>
       <c r="Y31" s="8">
-        <f t="shared" si="7"/>
-        <v>9997</v>
+        <f t="shared" si="8"/>
+        <v>11107</v>
       </c>
       <c r="Z31" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>110</v>
       </c>
       <c r="AA31" s="17">
@@ -19735,7 +19726,7 @@
       <c r="AD31" s="13"/>
       <c r="AE31" s="13">
         <f t="shared" si="19"/>
-        <v>9887</v>
+        <v>10997</v>
       </c>
       <c r="AF31" s="37"/>
       <c r="AG31" s="72"/>
@@ -19746,7 +19737,7 @@
         <v>35</v>
       </c>
       <c r="B32" s="15">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>73</v>
@@ -19756,11 +19747,11 @@
       </c>
       <c r="E32" s="6"/>
       <c r="F32" s="7">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G32" s="7">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H32" s="6"/>
       <c r="I32" s="27" t="s">
@@ -19778,19 +19769,19 @@
       <c r="N32" s="16"/>
       <c r="O32" s="13">
         <f t="shared" si="21"/>
-        <v>8450</v>
+        <v>10075</v>
       </c>
       <c r="P32" s="13">
         <f t="shared" si="22"/>
-        <v>5915</v>
+        <v>7052.5</v>
       </c>
       <c r="Q32" s="13">
         <f t="shared" si="14"/>
-        <v>2535</v>
+        <v>3022.5</v>
       </c>
       <c r="R32" s="13">
         <f t="shared" si="20"/>
-        <v>1950</v>
+        <v>2325</v>
       </c>
       <c r="S32" s="13">
         <f t="shared" si="18"/>
@@ -19799,26 +19790,26 @@
       <c r="T32" s="13"/>
       <c r="U32" s="8">
         <f t="shared" si="1"/>
-        <v>10400</v>
+        <v>12400</v>
       </c>
       <c r="V32" s="13">
         <f t="shared" si="15"/>
-        <v>5915</v>
+        <v>7052.5</v>
       </c>
       <c r="W32" s="13">
         <f t="shared" si="12"/>
-        <v>710</v>
+        <v>846</v>
       </c>
       <c r="X32" s="8">
-        <f t="shared" si="6"/>
-        <v>64</v>
+        <f t="shared" si="7"/>
+        <v>76</v>
       </c>
       <c r="Y32" s="8">
-        <f t="shared" si="7"/>
-        <v>9626</v>
+        <f t="shared" si="8"/>
+        <v>11478</v>
       </c>
       <c r="Z32" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>110</v>
       </c>
       <c r="AA32" s="17">
@@ -19830,7 +19821,7 @@
       <c r="AD32" s="13"/>
       <c r="AE32" s="13">
         <f t="shared" si="19"/>
-        <v>9516</v>
+        <v>11368</v>
       </c>
       <c r="AF32" s="37"/>
       <c r="AG32" s="72"/>
@@ -19841,7 +19832,7 @@
         <v>36</v>
       </c>
       <c r="B33" s="15">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>74</v>
@@ -19851,11 +19842,11 @@
       </c>
       <c r="E33" s="6"/>
       <c r="F33" s="7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G33" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="6"/>
       <c r="I33" s="27" t="s">
@@ -19873,19 +19864,19 @@
       <c r="N33" s="16"/>
       <c r="O33" s="13">
         <f t="shared" si="21"/>
-        <v>9715</v>
+        <v>10385</v>
       </c>
       <c r="P33" s="13">
         <f t="shared" si="22"/>
-        <v>6800.5</v>
+        <v>7269.4999999999991</v>
       </c>
       <c r="Q33" s="13">
         <f t="shared" si="14"/>
-        <v>2914.5</v>
+        <v>3115.5</v>
       </c>
       <c r="R33" s="13">
         <f t="shared" si="20"/>
-        <v>1885</v>
+        <v>2015</v>
       </c>
       <c r="S33" s="13">
         <f t="shared" si="18"/>
@@ -19894,26 +19885,26 @@
       <c r="T33" s="13"/>
       <c r="U33" s="8">
         <f t="shared" si="1"/>
-        <v>11600</v>
+        <v>12400</v>
       </c>
       <c r="V33" s="13">
         <f t="shared" si="15"/>
-        <v>6800.5</v>
+        <v>7269.4999999999991</v>
       </c>
       <c r="W33" s="13">
         <f t="shared" si="12"/>
-        <v>816</v>
+        <v>872</v>
       </c>
       <c r="X33" s="8">
-        <f t="shared" si="6"/>
-        <v>73</v>
+        <f t="shared" si="7"/>
+        <v>78</v>
       </c>
       <c r="Y33" s="8">
-        <f t="shared" si="7"/>
-        <v>10711</v>
+        <f t="shared" si="8"/>
+        <v>11450</v>
       </c>
       <c r="Z33" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>110</v>
       </c>
       <c r="AA33" s="17">
@@ -19924,7 +19915,7 @@
       <c r="AD33" s="13"/>
       <c r="AE33" s="13">
         <f t="shared" si="19"/>
-        <v>10601</v>
+        <v>11340</v>
       </c>
       <c r="AF33" s="37"/>
       <c r="AG33" s="72"/>
@@ -19935,7 +19926,7 @@
         <v>37</v>
       </c>
       <c r="B34" s="15">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>75</v>
@@ -19945,7 +19936,7 @@
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G34" s="7">
         <f t="shared" si="2"/>
@@ -19967,19 +19958,19 @@
       <c r="N34" s="16"/>
       <c r="O34" s="13">
         <f>L34*F34</f>
-        <v>10050</v>
+        <v>10385</v>
       </c>
       <c r="P34" s="13">
         <f t="shared" si="22"/>
-        <v>7035</v>
+        <v>7269.4999999999991</v>
       </c>
       <c r="Q34" s="13">
         <f t="shared" si="14"/>
-        <v>3015</v>
+        <v>3115.5</v>
       </c>
       <c r="R34" s="13">
         <f t="shared" si="20"/>
-        <v>1950</v>
+        <v>2015</v>
       </c>
       <c r="S34" s="13">
         <f t="shared" si="18"/>
@@ -19988,26 +19979,26 @@
       <c r="T34" s="13"/>
       <c r="U34" s="8">
         <f t="shared" si="1"/>
-        <v>12000</v>
+        <v>12400</v>
       </c>
       <c r="V34" s="13">
         <f t="shared" si="15"/>
-        <v>7035</v>
+        <v>7269.4999999999991</v>
       </c>
       <c r="W34" s="13">
         <f t="shared" si="12"/>
-        <v>844</v>
+        <v>872</v>
       </c>
       <c r="X34" s="8">
-        <f t="shared" si="6"/>
-        <v>76</v>
+        <f t="shared" si="7"/>
+        <v>78</v>
       </c>
       <c r="Y34" s="8">
-        <f t="shared" si="7"/>
-        <v>11080</v>
+        <f t="shared" si="8"/>
+        <v>11450</v>
       </c>
       <c r="Z34" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>110</v>
       </c>
       <c r="AA34" s="17">
@@ -20018,7 +20009,7 @@
       <c r="AD34" s="13"/>
       <c r="AE34" s="13">
         <f t="shared" si="19"/>
-        <v>10970</v>
+        <v>11340</v>
       </c>
       <c r="AF34" s="37"/>
       <c r="AG34" s="72"/>
@@ -20029,7 +20020,7 @@
         <v>38</v>
       </c>
       <c r="B35" s="15">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>76</v>
@@ -20037,11 +20028,11 @@
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
       <c r="F35" s="7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G35" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="27" t="s">
@@ -20059,19 +20050,19 @@
       <c r="N35" s="16"/>
       <c r="O35" s="13">
         <f t="shared" ref="O35:O38" si="23">L35*F35</f>
-        <v>8775</v>
+        <v>8450</v>
       </c>
       <c r="P35" s="13">
         <f t="shared" si="22"/>
-        <v>6142.5</v>
+        <v>5915</v>
       </c>
       <c r="Q35" s="13">
         <f t="shared" si="14"/>
-        <v>2632.5</v>
+        <v>2535</v>
       </c>
       <c r="R35" s="13">
         <f t="shared" si="20"/>
-        <v>2025</v>
+        <v>1950</v>
       </c>
       <c r="S35" s="13">
         <f t="shared" si="18"/>
@@ -20080,26 +20071,26 @@
       <c r="T35" s="13"/>
       <c r="U35" s="8">
         <f t="shared" si="1"/>
-        <v>10800</v>
+        <v>10400</v>
       </c>
       <c r="V35" s="13">
         <f t="shared" si="15"/>
-        <v>6142.5</v>
+        <v>5915</v>
       </c>
       <c r="W35" s="13">
         <f t="shared" si="12"/>
-        <v>737</v>
+        <v>710</v>
       </c>
       <c r="X35" s="8">
-        <f t="shared" si="6"/>
-        <v>66</v>
+        <f t="shared" si="7"/>
+        <v>64</v>
       </c>
       <c r="Y35" s="8">
-        <f t="shared" si="7"/>
-        <v>9997</v>
+        <f t="shared" si="8"/>
+        <v>9626</v>
       </c>
       <c r="Z35" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>110</v>
       </c>
       <c r="AA35" s="17">
@@ -20110,7 +20101,7 @@
       <c r="AD35" s="13"/>
       <c r="AE35" s="13">
         <f t="shared" si="19"/>
-        <v>9887</v>
+        <v>9516</v>
       </c>
       <c r="AF35" s="37"/>
       <c r="AG35" s="72"/>
@@ -20121,7 +20112,7 @@
         <v>39</v>
       </c>
       <c r="B36" s="15">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>77</v>
@@ -20129,7 +20120,7 @@
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
       <c r="F36" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G36" s="7">
         <f t="shared" si="2"/>
@@ -20151,19 +20142,19 @@
       <c r="N36" s="16"/>
       <c r="O36" s="13">
         <f t="shared" si="23"/>
-        <v>9135</v>
+        <v>9450</v>
       </c>
       <c r="P36" s="13">
         <f t="shared" si="22"/>
-        <v>6394.5</v>
+        <v>6615</v>
       </c>
       <c r="Q36" s="13">
         <f t="shared" si="14"/>
-        <v>2740.5</v>
+        <v>2835</v>
       </c>
       <c r="R36" s="13">
         <f t="shared" si="20"/>
-        <v>2465</v>
+        <v>2550</v>
       </c>
       <c r="S36" s="13">
         <f t="shared" si="18"/>
@@ -20172,26 +20163,26 @@
       <c r="T36" s="13"/>
       <c r="U36" s="8">
         <f t="shared" si="1"/>
-        <v>11600</v>
+        <v>12000</v>
       </c>
       <c r="V36" s="13">
         <f t="shared" si="15"/>
-        <v>6394.5</v>
+        <v>6615</v>
       </c>
       <c r="W36" s="13">
         <f t="shared" si="12"/>
-        <v>767</v>
+        <v>794</v>
       </c>
       <c r="X36" s="8">
-        <f t="shared" si="6"/>
-        <v>69</v>
+        <f t="shared" si="7"/>
+        <v>71</v>
       </c>
       <c r="Y36" s="8">
-        <f t="shared" si="7"/>
-        <v>10764</v>
+        <f t="shared" si="8"/>
+        <v>11135</v>
       </c>
       <c r="Z36" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>110</v>
       </c>
       <c r="AA36" s="17">
@@ -20202,7 +20193,7 @@
       <c r="AD36" s="13"/>
       <c r="AE36" s="13">
         <f t="shared" si="19"/>
-        <v>10654</v>
+        <v>11025</v>
       </c>
       <c r="AF36" s="37"/>
       <c r="AG36" s="72"/>
@@ -20213,7 +20204,7 @@
         <v>41</v>
       </c>
       <c r="B37" s="15">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>79</v>
@@ -20221,11 +20212,11 @@
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
       <c r="F37" s="7">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G37" s="7">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H37" s="6"/>
       <c r="I37" s="27" t="s">
@@ -20243,19 +20234,19 @@
       <c r="N37" s="16"/>
       <c r="O37" s="13">
         <f t="shared" si="23"/>
-        <v>7560</v>
+        <v>9765</v>
       </c>
       <c r="P37" s="13">
         <f t="shared" si="22"/>
-        <v>5292</v>
+        <v>6835.5</v>
       </c>
       <c r="Q37" s="13">
         <f t="shared" si="14"/>
-        <v>2268</v>
+        <v>2929.5</v>
       </c>
       <c r="R37" s="13">
         <f t="shared" si="20"/>
-        <v>2040</v>
+        <v>2635</v>
       </c>
       <c r="S37" s="13">
         <f t="shared" si="18"/>
@@ -20264,27 +20255,27 @@
       <c r="T37" s="13"/>
       <c r="U37" s="8">
         <f t="shared" si="1"/>
-        <v>9600</v>
+        <v>12400</v>
       </c>
       <c r="V37" s="13">
         <f t="shared" si="15"/>
-        <v>5292</v>
+        <v>6835.5</v>
       </c>
       <c r="W37" s="13">
         <f t="shared" si="12"/>
-        <v>635</v>
+        <v>820</v>
       </c>
       <c r="X37" s="8">
-        <f t="shared" si="6"/>
-        <v>57</v>
+        <f t="shared" si="7"/>
+        <v>74</v>
       </c>
       <c r="Y37" s="8">
-        <f t="shared" si="7"/>
-        <v>8908</v>
+        <f t="shared" si="8"/>
+        <v>11506</v>
       </c>
       <c r="Z37" s="11">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>110</v>
       </c>
       <c r="AA37" s="17">
         <v>110</v>
@@ -20294,7 +20285,7 @@
       <c r="AD37" s="13"/>
       <c r="AE37" s="13">
         <f t="shared" si="19"/>
-        <v>8908</v>
+        <v>11396</v>
       </c>
       <c r="AF37" s="37"/>
       <c r="AG37" s="72"/>
@@ -20305,7 +20296,7 @@
         <v>42</v>
       </c>
       <c r="B38" s="15">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>80</v>
@@ -20313,7 +20304,7 @@
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G38" s="7">
         <f t="shared" si="2"/>
@@ -20330,8 +20321,8 @@
         <v>60000</v>
       </c>
       <c r="L38" s="13">
-        <f>K38/30</f>
-        <v>2000</v>
+        <f>K38/31</f>
+        <v>1935.483870967742</v>
       </c>
       <c r="M38" s="16">
         <f t="shared" ref="M38:M43" si="24">R38/31</f>
@@ -20368,15 +20359,15 @@
         <v>0</v>
       </c>
       <c r="X38" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y38" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>60000</v>
       </c>
       <c r="Z38" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>200</v>
       </c>
       <c r="AA38" s="17">
@@ -20399,7 +20390,7 @@
         <v>43</v>
       </c>
       <c r="B39" s="15">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>81</v>
@@ -20407,7 +20398,7 @@
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G39" s="7">
         <f t="shared" si="2"/>
@@ -20422,8 +20413,8 @@
         <v>25000</v>
       </c>
       <c r="L39" s="13">
-        <f t="shared" ref="L39:L43" si="27">K39/30</f>
-        <v>833.33333333333337</v>
+        <f t="shared" ref="L39:L43" si="27">K39/31</f>
+        <v>806.45161290322585</v>
       </c>
       <c r="M39" s="16">
         <f t="shared" si="24"/>
@@ -20459,15 +20450,15 @@
         <v>0</v>
       </c>
       <c r="X39" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y39" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>25000</v>
       </c>
       <c r="Z39" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>130</v>
       </c>
       <c r="AA39" s="17">
@@ -20489,7 +20480,7 @@
         <v>44</v>
       </c>
       <c r="B40" s="15">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>82</v>
@@ -20499,9 +20490,9 @@
       </c>
       <c r="E40" s="6"/>
       <c r="F40" s="6">
-        <v>30</v>
-      </c>
-      <c r="G40" s="6">
+        <v>31</v>
+      </c>
+      <c r="G40" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -20515,7 +20506,7 @@
       </c>
       <c r="L40" s="13">
         <f t="shared" si="27"/>
-        <v>833.33333333333337</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="M40" s="16">
         <f t="shared" si="24"/>
@@ -20551,15 +20542,15 @@
         <v>0</v>
       </c>
       <c r="X40" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y40" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>25000</v>
       </c>
       <c r="Z40" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>130</v>
       </c>
       <c r="AA40" s="17">
@@ -20582,7 +20573,7 @@
         <v>45</v>
       </c>
       <c r="B41" s="15">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>84</v>
@@ -20590,9 +20581,9 @@
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
       <c r="F41" s="6">
-        <v>30</v>
-      </c>
-      <c r="G41" s="6">
+        <v>31</v>
+      </c>
+      <c r="G41" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -20606,7 +20597,7 @@
       </c>
       <c r="L41" s="13">
         <f t="shared" si="27"/>
-        <v>833.33333333333337</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="M41" s="16">
         <f t="shared" si="24"/>
@@ -20640,15 +20631,15 @@
         <v>0</v>
       </c>
       <c r="X41" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y41" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>25000</v>
       </c>
       <c r="Z41" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>130</v>
       </c>
       <c r="AA41" s="17">
@@ -20677,12 +20668,10 @@
       </c>
       <c r="D42" s="62"/>
       <c r="E42" s="62"/>
-      <c r="F42" s="62">
-        <v>0</v>
-      </c>
-      <c r="G42" s="62">
+      <c r="F42" s="62"/>
+      <c r="G42" s="7">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H42" s="62"/>
       <c r="I42" s="81"/>
@@ -20692,9 +20681,9 @@
       <c r="K42" s="62">
         <v>35000</v>
       </c>
-      <c r="L42" s="64">
+      <c r="L42" s="13">
         <f t="shared" si="27"/>
-        <v>1166.6666666666667</v>
+        <v>1129.0322580645161</v>
       </c>
       <c r="M42" s="65">
         <f t="shared" si="24"/>
@@ -20731,15 +20720,15 @@
         <v>0</v>
       </c>
       <c r="X42" s="64">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y42" s="64">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Z42" s="66">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA42" s="67">
@@ -20762,7 +20751,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="15">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>86</v>
@@ -20770,9 +20759,9 @@
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
       <c r="F43" s="6">
-        <v>30</v>
-      </c>
-      <c r="G43" s="6">
+        <v>31</v>
+      </c>
+      <c r="G43" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -20788,7 +20777,7 @@
       </c>
       <c r="L43" s="13">
         <f t="shared" si="27"/>
-        <v>2000</v>
+        <v>1935.483870967742</v>
       </c>
       <c r="M43" s="16">
         <f t="shared" si="24"/>
@@ -20825,15 +20814,15 @@
         <v>0</v>
       </c>
       <c r="X43" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y43" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>60000</v>
       </c>
       <c r="Z43" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>200</v>
       </c>
       <c r="AA43" s="17">
@@ -20856,7 +20845,7 @@
         <v>47</v>
       </c>
       <c r="B44" s="15">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>87</v>
@@ -20864,11 +20853,11 @@
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
       <c r="F44" s="6">
-        <v>30</v>
-      </c>
-      <c r="G44" s="6">
+        <v>29</v>
+      </c>
+      <c r="G44" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H44" s="6"/>
       <c r="I44" s="38"/>
@@ -20886,19 +20875,19 @@
       <c r="N44" s="16"/>
       <c r="O44" s="13">
         <f t="shared" si="29"/>
-        <v>10680</v>
+        <v>10324</v>
       </c>
       <c r="P44" s="13">
         <f t="shared" ref="P44:P47" si="33">O44*0.7</f>
-        <v>7475.9999999999991</v>
+        <v>7226.7999999999993</v>
       </c>
       <c r="Q44" s="13">
         <f t="shared" si="30"/>
-        <v>3204</v>
+        <v>3097.2</v>
       </c>
       <c r="R44" s="13">
         <f>M44*F44</f>
-        <v>1620</v>
+        <v>1566</v>
       </c>
       <c r="S44" s="13">
         <f>H44*(L44+M44)</f>
@@ -20907,26 +20896,26 @@
       <c r="T44" s="13"/>
       <c r="U44" s="13">
         <f t="shared" si="25"/>
-        <v>12300</v>
+        <v>11890</v>
       </c>
       <c r="V44" s="13">
         <f>P44</f>
-        <v>7475.9999999999991</v>
+        <v>7226.7999999999993</v>
       </c>
       <c r="W44" s="13">
         <f t="shared" si="31"/>
-        <v>897</v>
+        <v>867</v>
       </c>
       <c r="X44" s="13">
-        <f t="shared" si="6"/>
-        <v>81</v>
+        <f t="shared" si="7"/>
+        <v>78</v>
       </c>
       <c r="Y44" s="13">
-        <f t="shared" si="7"/>
-        <v>11322</v>
+        <f t="shared" si="8"/>
+        <v>10945</v>
       </c>
       <c r="Z44" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>110</v>
       </c>
       <c r="AA44" s="17">
@@ -20937,7 +20926,7 @@
       <c r="AD44" s="13"/>
       <c r="AE44" s="13">
         <f t="shared" si="28"/>
-        <v>11212</v>
+        <v>10835</v>
       </c>
       <c r="AF44" s="26"/>
       <c r="AG44" s="77"/>
@@ -20948,7 +20937,7 @@
         <v>48</v>
       </c>
       <c r="B45" s="15">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>88</v>
@@ -20956,11 +20945,11 @@
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6">
-        <v>29</v>
-      </c>
-      <c r="G45" s="6">
+        <v>28</v>
+      </c>
+      <c r="G45" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="38"/>
@@ -20978,19 +20967,19 @@
       <c r="N45" s="16"/>
       <c r="O45" s="13">
         <f t="shared" si="29"/>
-        <v>10324</v>
+        <v>9968</v>
       </c>
       <c r="P45" s="13">
         <f t="shared" si="33"/>
-        <v>7226.7999999999993</v>
+        <v>6977.5999999999995</v>
       </c>
       <c r="Q45" s="13">
         <f t="shared" si="30"/>
-        <v>3097.2</v>
+        <v>2990.4</v>
       </c>
       <c r="R45" s="13">
         <f t="shared" ref="R45:R47" si="34">M45*F45</f>
-        <v>1566</v>
+        <v>1512</v>
       </c>
       <c r="S45" s="13">
         <f>H45*(L45+M45)</f>
@@ -20999,26 +20988,26 @@
       <c r="T45" s="13"/>
       <c r="U45" s="13">
         <f t="shared" si="25"/>
-        <v>11890</v>
+        <v>11480</v>
       </c>
       <c r="V45" s="13">
         <f>P45</f>
-        <v>7226.7999999999993</v>
+        <v>6977.5999999999995</v>
       </c>
       <c r="W45" s="13">
         <f t="shared" si="31"/>
-        <v>867</v>
+        <v>837</v>
       </c>
       <c r="X45" s="13">
-        <f t="shared" si="6"/>
-        <v>78</v>
+        <f t="shared" si="7"/>
+        <v>75</v>
       </c>
       <c r="Y45" s="13">
-        <f t="shared" si="7"/>
-        <v>10945</v>
+        <f t="shared" si="8"/>
+        <v>10568</v>
       </c>
       <c r="Z45" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>110</v>
       </c>
       <c r="AA45" s="17">
@@ -21029,7 +21018,7 @@
       <c r="AD45" s="13"/>
       <c r="AE45" s="13">
         <f t="shared" si="28"/>
-        <v>10835</v>
+        <v>10458</v>
       </c>
       <c r="AF45" s="26"/>
       <c r="AG45" s="77"/>
@@ -21040,7 +21029,7 @@
         <v>49</v>
       </c>
       <c r="B46" s="15">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>89</v>
@@ -21048,11 +21037,11 @@
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6">
-        <v>28</v>
-      </c>
-      <c r="G46" s="6">
+        <v>26</v>
+      </c>
+      <c r="G46" s="7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H46" s="6"/>
       <c r="I46" s="27" t="s">
@@ -21072,19 +21061,19 @@
       <c r="N46" s="16"/>
       <c r="O46" s="13">
         <f t="shared" si="29"/>
-        <v>9352</v>
+        <v>8684</v>
       </c>
       <c r="P46" s="13">
         <f t="shared" si="33"/>
-        <v>6546.4</v>
+        <v>6078.7999999999993</v>
       </c>
       <c r="Q46" s="13">
         <f t="shared" si="30"/>
-        <v>2805.6</v>
+        <v>2605.1999999999998</v>
       </c>
       <c r="R46" s="13">
         <f t="shared" si="34"/>
-        <v>1848</v>
+        <v>1716</v>
       </c>
       <c r="S46" s="13">
         <f>H46*(L46+M46)</f>
@@ -21093,26 +21082,26 @@
       <c r="T46" s="13"/>
       <c r="U46" s="13">
         <f t="shared" si="25"/>
-        <v>11200</v>
+        <v>10400</v>
       </c>
       <c r="V46" s="13">
         <f>P46</f>
-        <v>6546.4</v>
+        <v>6078.7999999999993</v>
       </c>
       <c r="W46" s="13">
         <f t="shared" si="31"/>
-        <v>786</v>
+        <v>729</v>
       </c>
       <c r="X46" s="13">
-        <f t="shared" si="6"/>
-        <v>71</v>
+        <f t="shared" si="7"/>
+        <v>66</v>
       </c>
       <c r="Y46" s="13">
-        <f t="shared" si="7"/>
-        <v>10343</v>
+        <f t="shared" si="8"/>
+        <v>9605</v>
       </c>
       <c r="Z46" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>110</v>
       </c>
       <c r="AA46" s="17">
@@ -21124,7 +21113,7 @@
       <c r="AD46" s="13"/>
       <c r="AE46" s="13">
         <f t="shared" si="28"/>
-        <v>10233</v>
+        <v>9495</v>
       </c>
       <c r="AF46" s="26"/>
       <c r="AG46" s="77"/>
@@ -21135,7 +21124,7 @@
         <v>50</v>
       </c>
       <c r="B47" s="15">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>90</v>
@@ -21143,11 +21132,11 @@
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6">
-        <v>25</v>
-      </c>
-      <c r="G47" s="6">
+        <v>4</v>
+      </c>
+      <c r="G47" s="7">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H47" s="6"/>
       <c r="I47" s="27" t="s">
@@ -21167,19 +21156,19 @@
       <c r="N47" s="16"/>
       <c r="O47" s="13">
         <f t="shared" si="29"/>
-        <v>8125</v>
+        <v>1300</v>
       </c>
       <c r="P47" s="13">
         <f t="shared" si="33"/>
-        <v>5687.5</v>
+        <v>909.99999999999989</v>
       </c>
       <c r="Q47" s="13">
         <f t="shared" si="30"/>
-        <v>2437.5</v>
+        <v>390</v>
       </c>
       <c r="R47" s="13">
         <f t="shared" si="34"/>
-        <v>1875</v>
+        <v>300</v>
       </c>
       <c r="S47" s="13">
         <f>H47*(L47+M47)</f>
@@ -21188,26 +21177,26 @@
       <c r="T47" s="13"/>
       <c r="U47" s="13">
         <f t="shared" si="25"/>
-        <v>10000</v>
+        <v>1600</v>
       </c>
       <c r="V47" s="13">
         <f>P47</f>
-        <v>5687.5</v>
+        <v>909.99999999999989</v>
       </c>
       <c r="W47" s="13">
         <f t="shared" si="31"/>
-        <v>683</v>
+        <v>109</v>
       </c>
       <c r="X47" s="13">
-        <f t="shared" si="6"/>
-        <v>61</v>
+        <f t="shared" si="7"/>
+        <v>10</v>
       </c>
       <c r="Y47" s="13">
-        <f t="shared" si="7"/>
-        <v>9256</v>
+        <f t="shared" si="8"/>
+        <v>1481</v>
       </c>
       <c r="Z47" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA47" s="17">
@@ -21219,7 +21208,7 @@
       <c r="AD47" s="13"/>
       <c r="AE47" s="13">
         <f t="shared" si="28"/>
-        <v>9256</v>
+        <v>1481</v>
       </c>
       <c r="AF47" s="26"/>
       <c r="AG47" s="77"/>
@@ -21230,7 +21219,7 @@
         <v>51</v>
       </c>
       <c r="B48" s="15">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>91</v>
@@ -21238,11 +21227,11 @@
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
       <c r="F48" s="6">
-        <v>29</v>
-      </c>
-      <c r="G48" s="6">
+        <v>31</v>
+      </c>
+      <c r="G48" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="6"/>
       <c r="I48" s="27"/>
@@ -21253,8 +21242,8 @@
         <v>51000</v>
       </c>
       <c r="L48" s="13">
-        <f>K48/30</f>
-        <v>1700</v>
+        <f>K48/31</f>
+        <v>1645.1612903225807</v>
       </c>
       <c r="M48" s="13">
         <f>N48/30</f>
@@ -21263,15 +21252,15 @@
       <c r="N48" s="16"/>
       <c r="O48" s="13">
         <f t="shared" si="29"/>
-        <v>49300</v>
+        <v>51000</v>
       </c>
       <c r="P48" s="13">
         <f>O48*0.51</f>
-        <v>25143</v>
+        <v>26010</v>
       </c>
       <c r="Q48" s="13">
         <f>O48*0.49</f>
-        <v>24157</v>
+        <v>24990</v>
       </c>
       <c r="R48" s="13"/>
       <c r="S48" s="16">
@@ -21281,7 +21270,7 @@
       <c r="T48" s="13"/>
       <c r="U48" s="13">
         <f t="shared" si="25"/>
-        <v>49300</v>
+        <v>51000</v>
       </c>
       <c r="V48" s="13">
         <v>0</v>
@@ -21291,15 +21280,15 @@
         <v>0</v>
       </c>
       <c r="X48" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y48" s="13">
-        <f t="shared" si="7"/>
-        <v>49300</v>
+        <f t="shared" si="8"/>
+        <v>51000</v>
       </c>
       <c r="Z48" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>200</v>
       </c>
       <c r="AA48" s="17">
@@ -21310,7 +21299,7 @@
       <c r="AD48" s="13"/>
       <c r="AE48" s="13">
         <f t="shared" si="28"/>
-        <v>49100</v>
+        <v>50800</v>
       </c>
       <c r="AF48" s="37"/>
       <c r="AG48" s="77"/>
@@ -21321,7 +21310,7 @@
         <v>52</v>
       </c>
       <c r="B49" s="15">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>92</v>
@@ -21329,7 +21318,7 @@
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
       <c r="F49" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G49" s="7">
         <f t="shared" si="2"/>
@@ -21346,8 +21335,8 @@
         <v>60000</v>
       </c>
       <c r="L49" s="13">
-        <f t="shared" ref="L49:L50" si="35">K49/30</f>
-        <v>2000</v>
+        <f t="shared" ref="L49:L50" si="35">K49/31</f>
+        <v>1935.483870967742</v>
       </c>
       <c r="M49" s="16">
         <f>R49/30</f>
@@ -21384,11 +21373,11 @@
         <v>0</v>
       </c>
       <c r="X49" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y49" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>60000</v>
       </c>
       <c r="Z49" s="11"/>
@@ -21414,7 +21403,7 @@
         <v>53</v>
       </c>
       <c r="B50" s="15">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>93</v>
@@ -21424,11 +21413,11 @@
       </c>
       <c r="E50" s="6"/>
       <c r="F50" s="7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G50" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H50" s="6"/>
       <c r="I50" s="39"/>
@@ -21440,11 +21429,11 @@
       </c>
       <c r="L50" s="13">
         <f t="shared" si="35"/>
-        <v>533.33333333333337</v>
+        <v>516.12903225806451</v>
       </c>
       <c r="M50" s="16">
         <f>R50/30</f>
-        <v>256.66666666666669</v>
+        <v>248.11111111111114</v>
       </c>
       <c r="N50" s="16">
         <f>2000+1000+2000+700+2000</f>
@@ -21452,19 +21441,19 @@
       </c>
       <c r="O50" s="13">
         <f t="shared" si="29"/>
-        <v>16000.000000000002</v>
+        <v>14967.741935483871</v>
       </c>
       <c r="P50" s="13">
         <f>O50*0.7</f>
-        <v>11200</v>
+        <v>10477.419354838708</v>
       </c>
       <c r="Q50" s="13">
         <f t="shared" si="30"/>
-        <v>4800</v>
+        <v>4490.322580645161</v>
       </c>
       <c r="R50" s="13">
         <f>(1000+1000+1000+2000+700+2000)/30*F50</f>
-        <v>7700.0000000000009</v>
+        <v>7443.3333333333339</v>
       </c>
       <c r="S50" s="16">
         <f t="shared" si="18"/>
@@ -21473,26 +21462,26 @@
       <c r="T50" s="13"/>
       <c r="U50" s="13">
         <f t="shared" si="25"/>
-        <v>23700</v>
+        <v>22411.075268817203</v>
       </c>
       <c r="V50" s="13">
         <f>P50</f>
-        <v>11200</v>
+        <v>10477.419354838708</v>
       </c>
       <c r="W50" s="13">
         <f t="shared" si="31"/>
-        <v>1344</v>
+        <v>1257</v>
       </c>
       <c r="X50" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y50" s="8">
-        <f t="shared" si="7"/>
-        <v>22356</v>
+        <f t="shared" si="8"/>
+        <v>21154.075268817203</v>
       </c>
       <c r="Z50" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>130</v>
       </c>
       <c r="AA50" s="17">
@@ -21503,7 +21492,7 @@
       <c r="AD50" s="13"/>
       <c r="AE50" s="13">
         <f>U50-W50-X50-Z50-AB50</f>
-        <v>22226</v>
+        <v>21024.075268817203</v>
       </c>
       <c r="AF50" s="37"/>
       <c r="AG50" s="72"/>
@@ -21514,7 +21503,7 @@
         <v>54</v>
       </c>
       <c r="B51" s="15">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>94</v>
@@ -21522,7 +21511,7 @@
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
       <c r="F51" s="7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G51" s="7">
         <f t="shared" si="2"/>
@@ -21544,19 +21533,19 @@
       <c r="N51" s="16"/>
       <c r="O51" s="13">
         <f t="shared" si="29"/>
-        <v>8320</v>
+        <v>8640</v>
       </c>
       <c r="P51" s="13">
         <f t="shared" ref="P51" si="36">O51*0.7</f>
-        <v>5824</v>
+        <v>6048</v>
       </c>
       <c r="Q51" s="13">
         <f t="shared" si="30"/>
-        <v>2496</v>
+        <v>2592</v>
       </c>
       <c r="R51" s="13">
         <f>M51*F51</f>
-        <v>910</v>
+        <v>945</v>
       </c>
       <c r="S51" s="13">
         <f>H51*(L51+M51)</f>
@@ -21565,26 +21554,26 @@
       <c r="T51" s="13"/>
       <c r="U51" s="8">
         <f t="shared" ref="U51:U52" si="37">P51+Q51+S51+R51+T51</f>
-        <v>9230</v>
+        <v>9585</v>
       </c>
       <c r="V51" s="13">
         <f t="shared" ref="V51" si="38">P51</f>
-        <v>5824</v>
+        <v>6048</v>
       </c>
       <c r="W51" s="13">
         <f t="shared" si="31"/>
-        <v>699</v>
+        <v>726</v>
       </c>
       <c r="X51" s="8">
-        <f t="shared" si="6"/>
-        <v>63</v>
+        <f t="shared" si="7"/>
+        <v>65</v>
       </c>
       <c r="Y51" s="8">
-        <f t="shared" si="7"/>
-        <v>8468</v>
+        <f t="shared" si="8"/>
+        <v>8794</v>
       </c>
       <c r="Z51" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA51" s="17"/>
@@ -21593,7 +21582,7 @@
       <c r="AD51" s="13"/>
       <c r="AE51" s="13">
         <f>U51-W51-X51-Z51-AB51-AC51</f>
-        <v>8468</v>
+        <v>8794</v>
       </c>
       <c r="AF51" s="37"/>
       <c r="AG51" s="72"/>
@@ -21604,7 +21593,7 @@
         <v>55</v>
       </c>
       <c r="B52" s="19">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C52" s="20" t="s">
         <v>95</v>
@@ -21612,11 +21601,11 @@
       <c r="D52" s="20"/>
       <c r="E52" s="20"/>
       <c r="F52" s="20">
-        <v>10</v>
-      </c>
-      <c r="G52" s="20">
+        <v>13</v>
+      </c>
+      <c r="G52" s="7">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H52" s="20"/>
       <c r="I52" s="20"/>
@@ -21627,8 +21616,8 @@
         <v>22000</v>
       </c>
       <c r="L52" s="21">
-        <f>K52/30</f>
-        <v>733.33333333333337</v>
+        <f>K52/31</f>
+        <v>709.67741935483866</v>
       </c>
       <c r="M52" s="21">
         <f>N52/30</f>
@@ -21639,18 +21628,18 @@
       </c>
       <c r="O52" s="21">
         <f>L52*F52</f>
-        <v>7333.3333333333339</v>
+        <v>9225.8064516129034</v>
       </c>
       <c r="P52" s="21">
         <f>O52*1</f>
-        <v>7333.3333333333339</v>
+        <v>9225.8064516129034</v>
       </c>
       <c r="Q52" s="40">
         <v>0</v>
       </c>
       <c r="R52" s="21">
         <f>(N52)/30*F52</f>
-        <v>333.33333333333337</v>
+        <v>433.33333333333337</v>
       </c>
       <c r="S52" s="22">
         <f t="shared" ref="S52" si="39">(L52+M52)*H52</f>
@@ -21659,7 +21648,7 @@
       <c r="T52" s="21"/>
       <c r="U52" s="21">
         <f t="shared" si="37"/>
-        <v>7666.666666666667</v>
+        <v>9659.1397849462373</v>
       </c>
       <c r="V52" s="40">
         <v>0</v>
@@ -21669,12 +21658,12 @@
         <v>0</v>
       </c>
       <c r="X52" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y52" s="21">
         <f>U52-W52-X52</f>
-        <v>7666.666666666667</v>
+        <v>9659.1397849462373</v>
       </c>
       <c r="Z52" s="23">
         <f>IF(U52&gt;40000,200,IF(U52&gt;25000,150,IF(U52&gt;15000,130,IF(U52&gt;10000,110,0))))</f>
@@ -21688,7 +21677,7 @@
       <c r="AD52" s="40"/>
       <c r="AE52" s="21">
         <f>U52-W52-X52-Z52-AB52</f>
-        <v>7666.666666666667</v>
+        <v>9659.1397849462373</v>
       </c>
       <c r="AF52" s="41"/>
       <c r="AG52" s="72"/>
@@ -21704,44 +21693,44 @@
       <c r="E53" s="44"/>
       <c r="F53" s="44">
         <f>SUM(F3:F52)</f>
-        <v>1302</v>
+        <v>1361</v>
       </c>
       <c r="G53" s="44"/>
       <c r="H53" s="44">
         <f>SUM(H3:H52)</f>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I53" s="45"/>
       <c r="J53" s="45"/>
       <c r="K53" s="44"/>
       <c r="L53" s="44">
         <f>SUM(L3:L52)</f>
-        <v>27014.333333333332</v>
+        <v>26442.806451612902</v>
       </c>
       <c r="M53" s="44">
         <f>SUM(M3:M52)</f>
-        <v>3338.6666666666665</v>
+        <v>3300.4444444444448</v>
       </c>
       <c r="N53" s="44"/>
       <c r="O53" s="44">
         <f t="shared" ref="O53:Z53" si="40">SUM(O3:O52)</f>
-        <v>707967.66666666674</v>
+        <v>719101.54838709673</v>
       </c>
       <c r="P53" s="46">
         <f t="shared" si="40"/>
-        <v>517230.3666666667</v>
+        <v>526414.62580645154</v>
       </c>
       <c r="Q53" s="47">
         <f t="shared" si="40"/>
-        <v>190737.30000000002</v>
+        <v>192686.92258064516</v>
       </c>
       <c r="R53" s="47">
         <f t="shared" si="40"/>
-        <v>91922.333333333328</v>
+        <v>96559.860215053748</v>
       </c>
       <c r="S53" s="44">
         <f t="shared" si="40"/>
-        <v>3488.3333333333335</v>
+        <v>1000</v>
       </c>
       <c r="T53" s="47">
         <f t="shared" si="40"/>
@@ -21749,34 +21738,34 @@
       </c>
       <c r="U53" s="48">
         <f t="shared" si="40"/>
-        <v>803378.33333333326</v>
+        <v>816661.40860215062</v>
       </c>
       <c r="V53" s="48">
         <f t="shared" si="40"/>
-        <v>227687.36666666664</v>
+        <v>230292.81935483866</v>
       </c>
       <c r="W53" s="48">
         <f t="shared" si="40"/>
-        <v>27325</v>
+        <v>27637</v>
       </c>
       <c r="X53" s="48">
         <f t="shared" si="40"/>
-        <v>2450</v>
+        <v>2473</v>
       </c>
       <c r="Y53" s="48">
         <f t="shared" si="40"/>
-        <v>773603.33333333326</v>
+        <v>786551.40860215062</v>
       </c>
       <c r="Z53" s="48">
         <f t="shared" si="40"/>
-        <v>3900</v>
+        <v>4380</v>
       </c>
       <c r="AA53" s="49">
         <v>4400</v>
       </c>
       <c r="AB53" s="49">
         <f>SUM(AB3:AB51)</f>
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="AC53" s="49"/>
       <c r="AD53" s="49">
@@ -21785,7 +21774,7 @@
       </c>
       <c r="AE53" s="50">
         <f>SUM(AE3:AE52)</f>
-        <v>750703.33333333326</v>
+        <v>765171.40860215062</v>
       </c>
       <c r="AF53" s="37"/>
       <c r="AG53" s="72"/>
